--- a/V5.0_双人执行工作区/B_AI交付/02_看板/DB06/DB06_COMPONENT_MAP_V50.xlsx
+++ b/V5.0_双人执行工作区/B_AI交付/02_看板/DB06/DB06_COMPONENT_MAP_V50.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="组件映射" sheetId="1" r:id="R607d73c4df1f40b3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="组件映射" sheetId="1" r:id="R2a9fbecf80ca450f"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -160,7 +160,7 @@
         <x:color rgb="FFD0021B"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFDEBEC"/>
         </x:patternFill>
       </x:fill>
@@ -171,7 +171,7 @@
         <x:color rgb="FF8A5A00"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFFF4DF"/>
         </x:patternFill>
       </x:fill>
@@ -182,7 +182,7 @@
         <x:color rgb="FF8A5A00"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFFF4DF"/>
         </x:patternFill>
       </x:fill>
@@ -193,7 +193,7 @@
         <x:color rgb="FF166534"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFDCFCE7"/>
         </x:patternFill>
       </x:fill>
@@ -428,7 +428,7 @@
   <x:sheetData>
     <x:row r="1" ht="34" customHeight="1">
       <x:c r="A1" s="4" t="str">
-        <x:v>DB06 组件映射表｜2026-08-30</x:v>
+        <x:v>DB06 组件映射表｜2026-08-31</x:v>
       </x:c>
       <x:c r="B1" s="4"/>
       <x:c r="C1" s="4"/>
@@ -491,10 +491,10 @@
         <x:v>2025-12-31</x:v>
       </x:c>
       <x:c r="H3" s="22" t="str">
-        <x:v>PASS_SCOPE / BLOCKED_RELATION</x:v>
+        <x:v>PASS_RELATION / READY_B_REVIEW</x:v>
       </x:c>
       <x:c r="I3" s="22" t="str">
-        <x:v>字段与作用范围正确；组件1未接收月份筛选</x:v>
+        <x:v>字段与作用范围正确；双向关系已保存并清缓存，组件1/3均接收月份筛选</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="32" customHeight="1">
@@ -604,13 +604,13 @@
         <x:v>月份+周期主状态</x:v>
       </x:c>
       <x:c r="G7" s="23" t="str">
-        <x:v>预期1；实际660</x:v>
+        <x:v>2020-04、2023-10、2025-12均实测：1条</x:v>
       </x:c>
       <x:c r="H7" s="23" t="str">
-        <x:v>BLOCKED_A_MODEL_RELATION</x:v>
+        <x:v>PASS_RELATION / READY_B_REVIEW</x:v>
       </x:c>
       <x:c r="I7" s="23" t="str">
-        <x:v>A核查V50_dim_date→V50_MVP_cycle_state关系方向/生效状态</x:v>
+        <x:v>A于2026-08-31修复为双向；三个月份预检均为1条</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="32" customHeight="1">
@@ -741,7 +741,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6f74d690fc7947b7"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R633db76be04143a7"/>
   </x:tableParts>
 </x:worksheet>
 </file>